--- a/简易测式/价格.xlsx
+++ b/简易测式/价格.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaczev\Desktop\留档\花钱对比\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaczev\Documents\GitHub\dsh-KazMode\简易测式\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>输入</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>这个时间 输入命中0.05 输入未命中1.5 输出4.5</t>
+  </si>
+  <si>
+    <t>没有钱跑分，拿游戏项目的一个bug浅跑一下。单个样本没有很强的说服力。</t>
+  </si>
+  <si>
+    <t>初始情况都是相同的，拿github还原改动</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1016,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.3451327433628" customWidth="1"/>
@@ -1129,6 +1135,16 @@
     <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
